--- a/apps/docs/public/generated/examples/showcase/executive-board-pack/artifact/executive-board-pack.xlsx
+++ b/apps/docs/public/generated/examples/showcase/executive-board-pack/artifact/executive-board-pack.xlsx
@@ -9,7 +9,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t>Account</t>
   </si>
@@ -62,64 +62,73 @@
     <t>AMER</t>
   </si>
   <si>
+    <t>Fintech</t>
+  </si>
+  <si>
+    <t>Elouise Reichert</t>
+  </si>
+  <si>
+    <t>Risk is manageable if onboarding debt is reduced before procurement review.</t>
+  </si>
+  <si>
+    <t>Bluebird Health</t>
+  </si>
+  <si>
+    <t>EMEA</t>
+  </si>
+  <si>
     <t>Retail</t>
   </si>
   <si>
-    <t>Steve Dickens</t>
-  </si>
-  <si>
-    <t>Expansion path tied to a live rollout and executive sponsorship.</t>
-  </si>
-  <si>
-    <t>Bluebird Health</t>
-  </si>
-  <si>
-    <t>Carlton Ziemann</t>
-  </si>
-  <si>
-    <t>Risk is manageable if onboarding debt is reduced before procurement review.</t>
+    <t>Joshuah Conn</t>
+  </si>
+  <si>
+    <t>Operational adoption is strong and the account is positioned for expansion.</t>
   </si>
   <si>
     <t>Delta Retail Group</t>
   </si>
   <si>
-    <t>EMEA</t>
+    <t>APAC</t>
+  </si>
+  <si>
+    <t>Healthcare</t>
+  </si>
+  <si>
+    <t>Sean Lind Sr.</t>
+  </si>
+  <si>
+    <t>Healthy usage trend, but commercial alignment still needs work before renewal.</t>
+  </si>
+  <si>
+    <t>Cinder Labs</t>
+  </si>
+  <si>
+    <t>Amos Mayer</t>
+  </si>
+  <si>
+    <t>Atlas Commerce</t>
+  </si>
+  <si>
+    <t>Mr. Brian Nienow</t>
+  </si>
+  <si>
+    <t>Meridian Bio</t>
   </si>
   <si>
     <t>Manufacturing</t>
   </si>
   <si>
-    <t>Timmy Brakus</t>
-  </si>
-  <si>
-    <t>Cinder Labs</t>
-  </si>
-  <si>
-    <t>Fintech</t>
-  </si>
-  <si>
-    <t>Bridget Conn</t>
-  </si>
-  <si>
-    <t>Healthy usage trend, but commercial alignment still needs work before renewal.</t>
-  </si>
-  <si>
-    <t>Atlas Commerce</t>
-  </si>
-  <si>
-    <t>Maida Kassulke</t>
-  </si>
-  <si>
-    <t>Meridian Bio</t>
-  </si>
-  <si>
-    <t>Desiree Turner</t>
+    <t>Jeramy Doyle-Gusikowski</t>
   </si>
   <si>
     <t>Portfolio total</t>
   </si>
   <si>
     <t>Portfolio average</t>
+  </si>
+  <si>
+    <t>Portfolio max</t>
   </si>
 </sst>
 </file>
@@ -132,7 +141,7 @@
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -143,9 +152,17 @@
     </font>
     <font>
       <b/>
+      <color rgb="FF334155"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF1E3A8A"/>
+    </font>
+    <font>
+      <b/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -157,16 +174,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF0F172A"/>
+        <fgColor rgb="FF0B1220"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8FAFC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0E7FF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7F1D1D"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF7ED"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEE2E2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBEAFE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFF6FF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE9E9E9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCFCE7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0FDF4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE7F3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF2F8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -213,28 +293,28 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -249,6 +329,96 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="14" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -295,13 +465,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z9"/>
+  <dimension ref="A1:Z10"/>
   <sheetFormatPr defaultRowHeight="30"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
     <col min="3" max="3" width="19" customWidth="1"/>
-    <col min="4" max="4" width="21" customWidth="1"/>
+    <col min="4" max="4" width="28" customWidth="1"/>
     <col min="5" max="5" width="19" customWidth="1"/>
     <col min="6" max="6" width="17" customWidth="1"/>
     <col min="7" max="7" width="21" customWidth="1"/>
@@ -315,13 +485,13 @@
     <col min="15" max="15" width="83" customWidth="1"/>
     <col min="18" max="18" width="27" customWidth="1"/>
     <col min="19" max="19" width="15" customWidth="1"/>
-    <col min="20" max="20" width="21" customWidth="1"/>
+    <col min="20" max="20" width="28" customWidth="1"/>
     <col min="21" max="21" width="19" customWidth="1"/>
     <col min="22" max="22" width="21" customWidth="1"/>
     <col min="23" max="23" width="15" customWidth="1"/>
     <col min="24" max="24" width="15" customWidth="1"/>
     <col min="25" max="25" width="19" customWidth="1"/>
-    <col min="26" max="26" width="80" customWidth="1"/>
+    <col min="26" max="26" width="83" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -370,31 +540,31 @@
       <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="Z1" s="13" t="s">
         <v>14</v>
       </c>
     </row>
@@ -415,16 +585,16 @@
         <v>764759</v>
       </c>
       <c r="F2" s="4">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="G2" s="3">
         <f>ROUND((E2*F2),0)</f>
       </c>
       <c r="H2" s="3">
-        <v>841235</v>
+        <v>879473</v>
       </c>
       <c r="I2" s="4">
-        <v>0.98</v>
+        <v>1.03</v>
       </c>
       <c r="J2" s="5">
         <v>1436</v>
@@ -436,39 +606,39 @@
         <f>IF((J2&gt;0),(K2/J2),0)</f>
       </c>
       <c r="M2" s="5">
-        <v>88</v>
+        <v>65</v>
       </c>
       <c r="N2" s="7">
-        <v>46077</v>
+        <v>46074</v>
       </c>
       <c r="O2" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="R2" s="2" t="s">
+      <c r="R2" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="S2" s="2" t="s">
+      <c r="S2" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="T2" s="2" t="s">
+      <c r="T2" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="U2" s="3">
+      <c r="U2" s="15">
         <v>764759</v>
       </c>
-      <c r="V2" s="3">
-        <v>841235</v>
-      </c>
-      <c r="W2" s="4">
-        <v>0.98</v>
-      </c>
-      <c r="X2" s="5">
-        <v>88</v>
-      </c>
-      <c r="Y2" s="7">
-        <v>46077</v>
-      </c>
-      <c r="Z2" s="8" t="s">
+      <c r="V2" s="15">
+        <v>879473</v>
+      </c>
+      <c r="W2" s="16">
+        <v>1.03</v>
+      </c>
+      <c r="X2" s="17">
+        <v>65</v>
+      </c>
+      <c r="Y2" s="18">
+        <v>46074</v>
+      </c>
+      <c r="Z2" s="19" t="s">
         <v>19</v>
       </c>
     </row>
@@ -477,362 +647,328 @@
         <v>20</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E3" s="3">
-        <v>375205</v>
+        <v>509118</v>
       </c>
       <c r="F3" s="4">
-        <v>0.15</v>
+        <v>0.24</v>
       </c>
       <c r="G3" s="3">
         <f>ROUND((E3*F3),0)</f>
       </c>
       <c r="H3" s="3">
-        <v>431486</v>
+        <v>631306</v>
       </c>
       <c r="I3" s="4">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="J3" s="5">
-        <v>1494</v>
+        <v>568</v>
       </c>
       <c r="K3" s="5">
-        <v>1352</v>
+        <v>489</v>
       </c>
       <c r="L3" s="6">
         <f>IF((J3&gt;0),(K3/J3),0)</f>
       </c>
       <c r="M3" s="5">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N3" s="7">
-        <v>46104</v>
+        <v>46101</v>
       </c>
       <c r="O3" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="S3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R3" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="S3" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="T3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="U3" s="3">
-        <v>375205</v>
-      </c>
-      <c r="V3" s="3">
-        <v>431486</v>
-      </c>
-      <c r="W3" s="4">
-        <v>1.13</v>
-      </c>
-      <c r="X3" s="5">
-        <v>79</v>
-      </c>
-      <c r="Y3" s="7">
-        <v>46104</v>
-      </c>
-      <c r="Z3" s="8" t="s">
-        <v>22</v>
+      <c r="T3" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="U3" s="15">
+        <v>905243</v>
+      </c>
+      <c r="V3" s="15">
+        <v>1031977</v>
+      </c>
+      <c r="W3" s="16">
+        <v>0.97</v>
+      </c>
+      <c r="X3" s="17">
+        <v>60</v>
+      </c>
+      <c r="Y3" s="18">
+        <v>46153</v>
+      </c>
+      <c r="Z3" s="19" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E4" s="3">
-        <v>662698</v>
+        <v>1121839</v>
       </c>
       <c r="F4" s="4">
-        <v>0.22</v>
+        <v>0.05</v>
       </c>
       <c r="G4" s="3">
         <f>ROUND((E4*F4),0)</f>
       </c>
       <c r="H4" s="3">
-        <v>808492</v>
+        <v>1177931</v>
       </c>
       <c r="I4" s="4">
-        <v>0.98</v>
+        <v>1.12</v>
       </c>
       <c r="J4" s="5">
-        <v>1056</v>
+        <v>1858</v>
       </c>
       <c r="K4" s="5">
-        <v>1039</v>
+        <v>1469</v>
       </c>
       <c r="L4" s="6">
         <f>IF((J4&gt;0),(K4/J4),0)</f>
       </c>
       <c r="M4" s="5">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="N4" s="7">
-        <v>46131</v>
+        <v>46122</v>
       </c>
       <c r="O4" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="R4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="S4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="R4" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="S4" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="T4" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="U4" s="15">
+        <v>776661</v>
+      </c>
+      <c r="V4" s="15">
+        <v>807727</v>
+      </c>
+      <c r="W4" s="16">
+        <v>1.18</v>
+      </c>
+      <c r="X4" s="17">
+        <v>61</v>
+      </c>
+      <c r="Y4" s="18">
+        <v>46221</v>
+      </c>
+      <c r="Z4" s="19" t="s">
         <v>24</v>
-      </c>
-      <c r="T4" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="U4" s="3">
-        <v>662698</v>
-      </c>
-      <c r="V4" s="3">
-        <v>808492</v>
-      </c>
-      <c r="W4" s="4">
-        <v>0.98</v>
-      </c>
-      <c r="X4" s="5">
-        <v>68</v>
-      </c>
-      <c r="Y4" s="7">
-        <v>46131</v>
-      </c>
-      <c r="Z4" s="8" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>28</v>
-      </c>
       <c r="D5" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E5" s="3">
-        <v>931234</v>
+        <v>905243</v>
       </c>
       <c r="F5" s="4">
-        <v>0.06</v>
+        <v>0.14</v>
       </c>
       <c r="G5" s="3">
         <f>ROUND((E5*F5),0)</f>
       </c>
       <c r="H5" s="3">
-        <v>987108</v>
+        <v>1031977</v>
       </c>
       <c r="I5" s="4">
-        <v>1.05</v>
+        <v>0.97</v>
       </c>
       <c r="J5" s="5">
-        <v>1288</v>
+        <v>712</v>
       </c>
       <c r="K5" s="5">
-        <v>1144</v>
+        <v>638</v>
       </c>
       <c r="L5" s="6">
         <f>IF((J5&gt;0),(K5/J5),0)</f>
       </c>
       <c r="M5" s="5">
-        <v>92</v>
+        <v>60</v>
       </c>
       <c r="N5" s="7">
-        <v>46166</v>
+        <v>46153</v>
       </c>
       <c r="O5" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="R5" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="S5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="T5" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="U5" s="3">
-        <v>715007</v>
-      </c>
-      <c r="V5" s="3">
-        <v>765057</v>
-      </c>
-      <c r="W5" s="4">
-        <v>1.11</v>
-      </c>
-      <c r="X5" s="5">
-        <v>78</v>
-      </c>
-      <c r="Y5" s="7">
-        <v>46193</v>
-      </c>
-      <c r="Z5" s="8" t="s">
-        <v>19</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="R5" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="U5" s="21">
+        <f>SUM(U2:U4)</f>
+      </c>
+      <c r="V5" s="21">
+        <f>SUM(V2:V4)</f>
+      </c>
+      <c r="W5" s="20"/>
+      <c r="X5" s="20"/>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E6" s="3">
-        <v>715007</v>
+        <v>1089829</v>
       </c>
       <c r="F6" s="4">
-        <v>0.07</v>
+        <v>0.17</v>
       </c>
       <c r="G6" s="3">
         <f>ROUND((E6*F6),0)</f>
       </c>
       <c r="H6" s="3">
-        <v>765057</v>
+        <v>1275100</v>
       </c>
       <c r="I6" s="4">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="J6" s="5">
-        <v>1555</v>
+        <v>2110</v>
       </c>
       <c r="K6" s="5">
-        <v>1187</v>
+        <v>1724</v>
       </c>
       <c r="L6" s="6">
         <f>IF((J6&gt;0),(K6/J6),0)</f>
       </c>
       <c r="M6" s="5">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="N6" s="7">
-        <v>46193</v>
+        <v>46184</v>
       </c>
       <c r="O6" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="R6" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="S6" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="T6" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="U6" s="3">
-        <v>1006070</v>
-      </c>
-      <c r="V6" s="3">
-        <v>1167041</v>
-      </c>
-      <c r="W6" s="4">
-        <v>1.11</v>
-      </c>
-      <c r="X6" s="5">
-        <v>72</v>
-      </c>
-      <c r="Y6" s="7">
-        <v>46211</v>
-      </c>
-      <c r="Z6" s="8" t="s">
-        <v>22</v>
+      <c r="R6" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="U6" s="21">
+        <f>AVERAGE(U2:U4)</f>
+      </c>
+      <c r="V6" s="21">
+        <f>AVERAGE(V2:V4)</f>
+      </c>
+      <c r="W6" s="22">
+        <f>AVERAGE(W2:W4)</f>
+      </c>
+      <c r="X6" s="23">
+        <f>AVERAGE(X2:X4)</f>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E7" s="3">
-        <v>1006070</v>
+        <v>776661</v>
       </c>
       <c r="F7" s="4">
-        <v>0.16</v>
+        <v>0.04</v>
       </c>
       <c r="G7" s="3">
         <f>ROUND((E7*F7),0)</f>
       </c>
       <c r="H7" s="3">
-        <v>1167041</v>
+        <v>807727</v>
       </c>
       <c r="I7" s="4">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="J7" s="5">
-        <v>1643</v>
+        <v>1753</v>
       </c>
       <c r="K7" s="5">
-        <v>1468</v>
+        <v>1196</v>
       </c>
       <c r="L7" s="6">
         <f>IF((J7&gt;0),(K7/J7),0)</f>
       </c>
       <c r="M7" s="5">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="N7" s="7">
-        <v>46211</v>
+        <v>46221</v>
       </c>
       <c r="O7" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="R7" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="U7" s="10">
-        <f>SUM(U2:U6)</f>
-      </c>
-      <c r="V7" s="10">
-        <f>SUM(V2:V6)</f>
-      </c>
-      <c r="W7" s="11">
-        <f>AVERAGE(W2:W6)</f>
-      </c>
-      <c r="X7" s="12">
-        <f>AVERAGE(X2:X6)</f>
+        <v>24</v>
+      </c>
+      <c r="R7" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="U7" s="20"/>
+      <c r="V7" s="20"/>
+      <c r="W7" s="20"/>
+      <c r="X7" s="23">
+        <f>MAX(X2:X4)</f>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="9" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E8" s="10">
         <f>SUM(E2:E7)</f>
@@ -843,29 +979,12 @@
       <c r="H8" s="10">
         <f>SUM(H2:H7)</f>
       </c>
-      <c r="I8" s="11">
-        <f>AVERAGE(I2:I7)</f>
-      </c>
-      <c r="M8" s="12">
-        <f>AVERAGE(M2:M7)</f>
-      </c>
-      <c r="R8" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="U8" s="10">
-        <f>AVERAGE(U2:U6)</f>
-      </c>
-      <c r="V8" s="10">
-        <f>AVERAGE(V2:V6)</f>
-      </c>
-      <c r="W8" s="9"/>
-      <c r="X8" s="12">
-        <f>MAX(X2:X6)</f>
-      </c>
+      <c r="I8" s="9"/>
+      <c r="M8" s="9"/>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="9" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E9" s="10">
         <f>AVERAGE(E2:E7)</f>
@@ -876,8 +995,22 @@
       <c r="H9" s="10">
         <f>AVERAGE(H2:H7)</f>
       </c>
-      <c r="I9" s="9"/>
+      <c r="I9" s="11">
+        <f>AVERAGE(I2:I7)</f>
+      </c>
       <c r="M9" s="12">
+        <f>AVERAGE(M2:M7)</f>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="E10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="9"/>
+      <c r="M10" s="12">
         <f>MAX(M2:M7)</f>
       </c>
     </row>
@@ -898,7 +1031,7 @@
       <formula>($M2&gt;=85)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="W2:W6">
+  <conditionalFormatting sqref="W2:W4">
     <cfRule type="expression" dxfId="0" priority="5">
       <formula>($F2&lt;1)</formula>
     </cfRule>
@@ -906,7 +1039,7 @@
       <formula>($F2&gt;=1.1)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="X2:X6">
+  <conditionalFormatting sqref="X2:X4">
     <cfRule type="expression" dxfId="2" priority="7">
       <formula>($G2&lt;70)</formula>
     </cfRule>
@@ -932,246 +1065,267 @@
     <col min="10" max="10" width="21" customWidth="1"/>
     <col min="11" max="11" width="15" customWidth="1"/>
     <col min="12" max="12" width="15" customWidth="1"/>
-    <col min="15" max="15" width="12" customWidth="1"/>
-    <col min="16" max="16" width="16" customWidth="1"/>
-    <col min="17" max="17" width="18" customWidth="1"/>
+    <col min="15" max="15" width="27" customWidth="1"/>
+    <col min="16" max="16" width="19" customWidth="1"/>
+    <col min="17" max="17" width="21" customWidth="1"/>
     <col min="18" max="18" width="15" customWidth="1"/>
     <col min="19" max="19" width="15" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" s="38" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2" s="26">
         <v>764759</v>
       </c>
-      <c r="C2" s="3">
-        <v>841235</v>
-      </c>
-      <c r="D2" s="4">
-        <v>0.98</v>
-      </c>
-      <c r="E2" s="5">
-        <v>88</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I2" s="3">
-        <v>662698</v>
-      </c>
-      <c r="J2" s="3">
-        <v>808492</v>
-      </c>
-      <c r="K2" s="4">
-        <v>0.98</v>
-      </c>
-      <c r="L2" s="5">
-        <v>68</v>
-      </c>
-      <c r="O2" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="P2" s="10">
-        <f>SUM(P2:P1)</f>
-      </c>
-      <c r="Q2" s="10">
-        <f>SUM(Q2:Q1)</f>
-      </c>
-      <c r="R2" s="11">
-        <f>AVERAGE(R2:R1)</f>
-      </c>
-      <c r="S2" s="12">
-        <f>AVERAGE(S2:S1)</f>
+      <c r="C2" s="26">
+        <v>879473</v>
+      </c>
+      <c r="D2" s="27">
+        <v>1.03</v>
+      </c>
+      <c r="E2" s="28">
+        <v>65</v>
+      </c>
+      <c r="H2" s="34" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" s="35">
+        <v>509118</v>
+      </c>
+      <c r="J2" s="35">
+        <v>631306</v>
+      </c>
+      <c r="K2" s="36">
+        <v>1.08</v>
+      </c>
+      <c r="L2" s="37">
+        <v>80</v>
+      </c>
+      <c r="O2" s="39" t="s">
+        <v>25</v>
+      </c>
+      <c r="P2" s="40">
+        <v>1121839</v>
+      </c>
+      <c r="Q2" s="40">
+        <v>1177931</v>
+      </c>
+      <c r="R2" s="41">
+        <v>1.12</v>
+      </c>
+      <c r="S2" s="42">
+        <v>92</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" s="3">
-        <v>375205</v>
-      </c>
-      <c r="C3" s="3">
-        <v>431486</v>
-      </c>
-      <c r="D3" s="4">
-        <v>1.13</v>
-      </c>
-      <c r="E3" s="5">
-        <v>79</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I3" s="3">
-        <v>931234</v>
-      </c>
-      <c r="J3" s="3">
-        <v>987108</v>
-      </c>
-      <c r="K3" s="4">
+      <c r="A3" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" s="26">
+        <v>905243</v>
+      </c>
+      <c r="C3" s="26">
+        <v>1031977</v>
+      </c>
+      <c r="D3" s="27">
+        <v>0.97</v>
+      </c>
+      <c r="E3" s="28">
+        <v>60</v>
+      </c>
+      <c r="H3" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="I3" s="35">
+        <v>1089829</v>
+      </c>
+      <c r="J3" s="35">
+        <v>1275100</v>
+      </c>
+      <c r="K3" s="36">
         <v>1.05</v>
       </c>
-      <c r="L3" s="5">
-        <v>92</v>
-      </c>
-      <c r="O3" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="P3" s="10">
-        <f>AVERAGE(P2:P1)</f>
-      </c>
-      <c r="Q3" s="10">
-        <f>AVERAGE(Q2:Q1)</f>
-      </c>
-      <c r="R3" s="9"/>
-      <c r="S3" s="12">
-        <f>MAX(S2:S1)</f>
+      <c r="L3" s="37">
+        <v>83</v>
+      </c>
+      <c r="O3" s="39" t="s">
+        <v>34</v>
+      </c>
+      <c r="P3" s="40">
+        <v>776661</v>
+      </c>
+      <c r="Q3" s="40">
+        <v>807727</v>
+      </c>
+      <c r="R3" s="41">
+        <v>1.18</v>
+      </c>
+      <c r="S3" s="42">
+        <v>61</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B4" s="3">
-        <v>715007</v>
-      </c>
-      <c r="C4" s="3">
-        <v>765057</v>
-      </c>
-      <c r="D4" s="4">
-        <v>1.11</v>
-      </c>
-      <c r="E4" s="5">
-        <v>78</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I4" s="3">
-        <v>1006070</v>
-      </c>
-      <c r="J4" s="3">
-        <v>1167041</v>
-      </c>
-      <c r="K4" s="4">
-        <v>1.11</v>
-      </c>
-      <c r="L4" s="5">
-        <v>72</v>
-      </c>
+      <c r="A4" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="30">
+        <f>SUM(B2:B3)</f>
+      </c>
+      <c r="C4" s="30">
+        <f>SUM(C2:C3)</f>
+      </c>
+      <c r="D4" s="29"/>
+      <c r="E4" s="29"/>
+      <c r="H4" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="I4" s="30">
+        <f>SUM(I2:I3)</f>
+      </c>
+      <c r="J4" s="30">
+        <f>SUM(J2:J3)</f>
+      </c>
+      <c r="K4" s="29"/>
+      <c r="L4" s="29"/>
+      <c r="O4" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="P4" s="30">
+        <f>SUM(P2:P3)</f>
+      </c>
+      <c r="Q4" s="30">
+        <f>SUM(Q2:Q3)</f>
+      </c>
+      <c r="R4" s="29"/>
+      <c r="S4" s="29"/>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5" s="10">
-        <f>SUM(B2:B4)</f>
-      </c>
-      <c r="C5" s="10">
-        <f>SUM(C2:C4)</f>
-      </c>
-      <c r="D5" s="11">
-        <f>AVERAGE(D2:D4)</f>
-      </c>
-      <c r="E5" s="12">
-        <f>AVERAGE(E2:E4)</f>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="I5" s="10">
-        <f>SUM(I2:I4)</f>
-      </c>
-      <c r="J5" s="10">
-        <f>SUM(J2:J4)</f>
-      </c>
-      <c r="K5" s="11">
-        <f>AVERAGE(K2:K4)</f>
-      </c>
-      <c r="L5" s="12">
-        <f>AVERAGE(L2:L4)</f>
+      <c r="A5" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" s="30">
+        <f>AVERAGE(B2:B3)</f>
+      </c>
+      <c r="C5" s="30">
+        <f>AVERAGE(C2:C3)</f>
+      </c>
+      <c r="D5" s="31">
+        <f>AVERAGE(D2:D3)</f>
+      </c>
+      <c r="E5" s="32">
+        <f>AVERAGE(E2:E3)</f>
+      </c>
+      <c r="H5" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="I5" s="30">
+        <f>AVERAGE(I2:I3)</f>
+      </c>
+      <c r="J5" s="30">
+        <f>AVERAGE(J2:J3)</f>
+      </c>
+      <c r="K5" s="31">
+        <f>AVERAGE(K2:K3)</f>
+      </c>
+      <c r="L5" s="32">
+        <f>AVERAGE(L2:L3)</f>
+      </c>
+      <c r="O5" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="P5" s="30">
+        <f>AVERAGE(P2:P3)</f>
+      </c>
+      <c r="Q5" s="30">
+        <f>AVERAGE(Q2:Q3)</f>
+      </c>
+      <c r="R5" s="31">
+        <f>AVERAGE(R2:R3)</f>
+      </c>
+      <c r="S5" s="32">
+        <f>AVERAGE(S2:S3)</f>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="B6" s="10">
-        <f>AVERAGE(B2:B4)</f>
-      </c>
-      <c r="C6" s="10">
-        <f>AVERAGE(C2:C4)</f>
-      </c>
-      <c r="D6" s="9"/>
-      <c r="E6" s="12">
-        <f>MAX(E2:E4)</f>
-      </c>
-      <c r="H6" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="I6" s="10">
-        <f>AVERAGE(I2:I4)</f>
-      </c>
-      <c r="J6" s="10">
-        <f>AVERAGE(J2:J4)</f>
-      </c>
-      <c r="K6" s="9"/>
-      <c r="L6" s="12">
-        <f>MAX(L2:L4)</f>
+      <c r="A6" s="29" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" s="29"/>
+      <c r="C6" s="29"/>
+      <c r="D6" s="29"/>
+      <c r="E6" s="32">
+        <f>MAX(E2:E3)</f>
+      </c>
+      <c r="H6" s="29" t="s">
+        <v>39</v>
+      </c>
+      <c r="I6" s="29"/>
+      <c r="J6" s="29"/>
+      <c r="K6" s="29"/>
+      <c r="L6" s="32">
+        <f>MAX(L2:L3)</f>
+      </c>
+      <c r="O6" s="29" t="s">
+        <v>39</v>
+      </c>
+      <c r="P6" s="29"/>
+      <c r="Q6" s="29"/>
+      <c r="R6" s="29"/>
+      <c r="S6" s="32">
+        <f>MAX(S2:S3)</f>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D2:D4">
+  <conditionalFormatting sqref="D2:D3">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>($D2&lt;1)</formula>
     </cfRule>
@@ -1179,7 +1333,7 @@
       <formula>($D2&gt;=1.1)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E4">
+  <conditionalFormatting sqref="E2:E3">
     <cfRule type="expression" dxfId="2" priority="3">
       <formula>($E2&lt;70)</formula>
     </cfRule>
@@ -1187,7 +1341,7 @@
       <formula>($E2&gt;=85)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K4">
+  <conditionalFormatting sqref="K2:K3">
     <cfRule type="expression" dxfId="0" priority="5">
       <formula>($D2&lt;1)</formula>
     </cfRule>
@@ -1195,11 +1349,27 @@
       <formula>($D2&gt;=1.1)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L4">
+  <conditionalFormatting sqref="L2:L3">
     <cfRule type="expression" dxfId="2" priority="7">
       <formula>($E2&lt;70)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="1" priority="8">
+      <formula>($E2&gt;=85)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R2:R3">
+    <cfRule type="expression" dxfId="0" priority="9">
+      <formula>($D2&lt;1)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="10">
+      <formula>($D2&gt;=1.1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S2:S3">
+    <cfRule type="expression" dxfId="2" priority="11">
+      <formula>($E2&lt;70)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="12">
       <formula>($E2&gt;=85)</formula>
     </cfRule>
   </conditionalFormatting>
